--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,130 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128262957</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gravfisktjärn, Henån, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>407832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6961155</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128262957</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128262957</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128262957</v>
       </c>
       <c r="B3" t="n">
-        <v>57698</v>
+        <v>57702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128262957</v>
       </c>
       <c r="B3" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109952831</v>
+        <v>128262957</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,18 +710,22 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gravfisktjärn, Hjd</t>
+          <t>Gravfisktjärn, Henån, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408068.3476095438</v>
+        <v>407832</v>
       </c>
       <c r="R2" t="n">
-        <v>6960933.683372431</v>
+        <v>6961155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,27 +799,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128262957</v>
+        <v>109952831</v>
       </c>
       <c r="B3" t="n">
-        <v>57729</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,22 +834,18 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gravfisktjärn, Henån, Storsjö, Hjd</t>
+          <t>Gravfisktjärn, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407832</v>
+        <v>408068</v>
       </c>
       <c r="R3" t="n">
-        <v>6961155</v>
+        <v>6960934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34271-2022 artfynd.xlsx
+++ b/artfynd/A 34271-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128262957</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109952831</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>